--- a/results/final_N33_v5/Trend_Method_Comparison/Excel/MMK_Analysis/MMK_vs_MK_Comparison.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Excel/MMK_Analysis/MMK_vs_MK_Comparison.xlsx
@@ -469,9 +469,9 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
@@ -751,14 +751,14 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>32.57076322410779</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.043880972823945</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>k=10(ρ=+0.405)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -853,14 +853,14 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>34</v>
+        <v>25.59</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>1.328398</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.471); k=9(ρ=−0.494)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>k=2(ρ=−0.357); k=3(ρ=−0.497); k=6(ρ=+0.375); k=9(ρ=−0.402)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>k=3(ρ=−0.435); k=9(ρ=−0.526)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>k=3(ρ=−0.596); k=6(ρ=+0.409); k=9(ρ=−0.385)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.509)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>k=3(ρ=−0.358); k=9(ρ=−0.480)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=−0.373); k=4(ρ=+0.357); k=5(ρ=−0.426); k=6(ρ=+0.377); k=7(ρ=−0.353); k=9(ρ=−0.470); k=11(ρ=−0.361)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.576)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>k=2(ρ=−0.342)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
@@ -2077,14 +2077,14 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.582); k=2(ρ=+0.361); k=9(ρ=−0.432); k=10(ρ=−0.351)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.362)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -2281,14 +2281,14 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.360)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -2383,14 +2383,14 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>k=1(ρ=+0.376)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>k=9(ρ=−0.382); k=11(ρ=+0.341)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>k=1(ρ=−0.397); k=5(ρ=−0.397); k=9(ρ=−0.445)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>k=6(ρ=−0.460); k=7(ρ=+0.411); k=9(ρ=−0.672)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
@@ -3403,14 +3403,14 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>31.9728189685143</v>
+        <v>33</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.032126695881812</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>k=6(ρ=+0.384); k=10(ρ=−0.479)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>k=10(ρ=−0.353)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
@@ -3607,14 +3607,14 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>30.04350146698373</v>
+        <v>19.93</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.098407255767618</v>
+        <v>1.656195</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>k=2(ρ=+0.405); k=6(ρ=+0.350)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>k=11(ρ=−0.404)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
